--- a/hira_material_automation/output/monthly/202601_202609__all_suture_anchor__040021__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__all_suture_anchor__040021__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04T22:53:47</t>
+          <t>2026-09-14T23:45:24</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fb14a78e6192c45acd91915579429492d3afbd53471f9d4da3b85a6abf5c9450</t>
+          <t>a852947faffa9865a371ed2c12ef42fd4fc150420fa084672095a9df4e18345d</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202609__all_suture_anchor__040021__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__all_suture_anchor__040021__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14T23:45:24</t>
+          <t>2026-09-24T23:48:45</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a852947faffa9865a371ed2c12ef42fd4fc150420fa084672095a9df4e18345d</t>
+          <t>3bdd09b907e321e1ea92620a873389c9d12a733f04f4a3f626d2e96b4c31b76f</t>
         </is>
       </c>
     </row>
